--- a/data/trans_camb/P16A13-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A13-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,4</t>
+          <t>-1,41; 4,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,93</t>
+          <t>-1,33; 3,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 7,0</t>
+          <t>1,68; 6,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 7,79</t>
+          <t>1,13; 7,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,1</t>
+          <t>-0,95; 4,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,3</t>
+          <t>0,26; 4,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 4,63</t>
+          <t>0,38; 4,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,23</t>
+          <t>-0,69; 3,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,86</t>
+          <t>1,58; 4,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 229,45</t>
+          <t>-36,2; 209,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 184,51</t>
+          <t>-33,57; 196,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,78; 377,39</t>
+          <t>30,29; 338,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,2; 833,36</t>
+          <t>14,09; 802,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,47; 499,75</t>
+          <t>-44,69; 468,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 468,52</t>
+          <t>-4,57; 605,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 237,14</t>
+          <t>7,11; 231,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 186,23</t>
+          <t>-22,99; 158,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,32; 259,86</t>
+          <t>42,82; 286,16</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,59</t>
+          <t>-1,48; 3,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,54</t>
+          <t>-1,28; 3,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,13</t>
+          <t>0,7; 6,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 5,26</t>
+          <t>-1,46; 4,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 4,53</t>
+          <t>-1,7; 4,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,5</t>
+          <t>-0,6; 4,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,44</t>
+          <t>-0,6; 3,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,06</t>
+          <t>-0,79; 3,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,55</t>
+          <t>0,79; 4,32</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,16; 351,92</t>
+          <t>-54,11; 261,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,84; 298,15</t>
+          <t>-40,66; 344,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,91; 497,08</t>
+          <t>3,54; 461,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 289,2</t>
+          <t>-38,54; 282,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 234,14</t>
+          <t>-46,48; 200,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 240,68</t>
+          <t>-17,8; 219,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 181,46</t>
+          <t>-18,46; 188,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 162,49</t>
+          <t>-24,94; 164,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,12; 261,69</t>
+          <t>22,7; 249,24</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,43</t>
+          <t>-0,77; 3,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,88</t>
+          <t>-1,12; 2,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 6,95</t>
+          <t>-1,05; 7,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 3,29</t>
+          <t>-5,14; 3,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 6,97</t>
+          <t>-4,27; 6,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 10,48</t>
+          <t>0,62; 10,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,73</t>
+          <t>-0,94; 2,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,88</t>
+          <t>-1,07; 3,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 6,9</t>
+          <t>-1,02; 6,74</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 228,89</t>
+          <t>-32,62; 225,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,45; 207,63</t>
+          <t>-39,45; 225,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 387,02</t>
+          <t>-30,94; 402,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,3; 129,38</t>
+          <t>-65,45; 123,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,27; 227,43</t>
+          <t>-61,91; 218,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 350,95</t>
+          <t>3,0; 322,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 139,45</t>
+          <t>-27,17; 130,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 136,77</t>
+          <t>-31,3; 152,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 275,86</t>
+          <t>-22,76; 271,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,98</t>
+          <t>0,56; 4,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,32</t>
+          <t>-2,26; 0,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,98</t>
+          <t>1,9; 5,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,58</t>
+          <t>-0,39; 3,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,54</t>
+          <t>-0,93; 2,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,97</t>
+          <t>-0,64; 5,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,19</t>
+          <t>0,69; 3,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,8</t>
+          <t>-1,39; 0,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,51</t>
+          <t>0,86; 4,36</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,65; 158,51</t>
+          <t>13,82; 169,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 16,77</t>
+          <t>-59,51; 13,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,94; 210,73</t>
+          <t>49,34; 216,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 157,74</t>
+          <t>-14,05; 150,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 115,52</t>
+          <t>-25,14; 134,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 217,85</t>
+          <t>-8,18; 215,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,34; 121,55</t>
+          <t>19,18; 123,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-36,29; 33,35</t>
+          <t>-39,41; 30,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>35,12; 177,03</t>
+          <t>34,96; 170,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,33</t>
+          <t>-1,61; 3,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,59</t>
+          <t>-1,52; 3,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 8,43</t>
+          <t>1,14; 8,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,18</t>
+          <t>1,47; 6,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,43</t>
+          <t>-1,6; 2,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,39</t>
+          <t>4,08; 10,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,46</t>
+          <t>0,82; 4,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,43</t>
+          <t>-0,62; 2,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,77</t>
+          <t>4,39; 8,68</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,93; 170,39</t>
+          <t>-38,96; 217,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 192,28</t>
+          <t>-35,8; 179,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19,66; 406,2</t>
+          <t>13,29; 369,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28,69; 297,1</t>
+          <t>32,69; 328,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,53; 117,02</t>
+          <t>-41,05; 121,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>116,13; 509,74</t>
+          <t>95,53; 508,57</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,64; 196,19</t>
+          <t>18,23; 192,67</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 106,02</t>
+          <t>-19,0; 103,21</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>103,04; 387,88</t>
+          <t>115,34; 372,61</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,28</t>
+          <t>-0,63; 3,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,13</t>
+          <t>-1,47; 0,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,8</t>
+          <t>-0,77; 2,92</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,31</t>
+          <t>-1,18; 2,33</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,84</t>
+          <t>-1,61; 1,86</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,52</t>
+          <t>3,38; 7,46</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,17</t>
+          <t>-0,8; 2,38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,39</t>
+          <t>-1,6; 1,35</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,85</t>
+          <t>2,64; 5,96</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-80,21; —</t>
+          <t>-97,37; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 61,3</t>
+          <t>-21,97; 62,79</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 49,51</t>
+          <t>-30,81; 51,67</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>64,34; 197,46</t>
+          <t>60,16; 198,84</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 65,56</t>
+          <t>-17,45; 75,26</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 44,93</t>
+          <t>-34,98; 42,17</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>51,96; 184,39</t>
+          <t>53,54; 190,76</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,4</t>
+          <t>0,52; 2,32</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,05</t>
+          <t>-0,54; 1,09</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,47</t>
+          <t>1,98; 4,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,76</t>
+          <t>0,74; 2,78</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,51</t>
+          <t>-0,43; 1,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,41</t>
+          <t>2,8; 5,36</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,32</t>
+          <t>0,95; 2,3</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,98</t>
+          <t>-0,26; 0,97</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,72</t>
+          <t>2,83; 4,63</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>18,17; 106,38</t>
+          <t>17,31; 101,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 46,87</t>
+          <t>-18,28; 48,34</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>62,82; 193,92</t>
+          <t>69,21; 188,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17,05; 87,34</t>
+          <t>18,01; 87,86</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 47,28</t>
+          <t>-10,49; 45,28</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>73,61; 173,09</t>
+          <t>72,17; 166,58</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,71; 80,08</t>
+          <t>28,16; 81,38</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 34,76</t>
+          <t>-7,65; 33,83</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>85,62; 166,35</t>
+          <t>85,87; 167,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A13-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A13-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>3,66</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>2,66</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>3,09</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,45</t>
+          <t>-1,33; 4,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,89</t>
+          <t>-1,52; 3,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,7</t>
+          <t>0,88; 6,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,63</t>
+          <t>1,26; 7,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,3</t>
+          <t>-1,21; 4,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,53</t>
+          <t>0,53; 4,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,56</t>
+          <t>0,35; 4,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,08</t>
+          <t>-0,66; 3,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,85</t>
+          <t>1,5; 4,66</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128,31%</t>
+          <t>115,49%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>134,67%</t>
+          <t>142,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>121,83%</t>
+          <t>116,16%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,2; 209,59</t>
+          <t>-35,95; 201,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 196,02</t>
+          <t>-38,46; 180,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,29; 338,59</t>
+          <t>13,69; 304,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,09; 802,58</t>
+          <t>25,86; 1114,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,69; 468,0</t>
+          <t>-48,86; 535,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 605,98</t>
+          <t>6,87; 642,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 231,26</t>
+          <t>6,16; 250,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 158,85</t>
+          <t>-23,45; 155,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,82; 286,16</t>
+          <t>38,84; 252,35</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>3,34</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>2,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,54</t>
+          <t>-1,67; 3,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,78</t>
+          <t>-1,68; 3,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,07</t>
+          <t>0,97; 5,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,98</t>
+          <t>-1,28; 5,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 4,07</t>
+          <t>-1,44; 4,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,17</t>
+          <t>-1,11; 3,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,38</t>
+          <t>-0,6; 3,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,08</t>
+          <t>-0,69; 3,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,32</t>
+          <t>0,9; 4,35</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153,53%</t>
+          <t>146,69%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>102,0%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-54,11; 261,79</t>
+          <t>-54,43; 307,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 344,81</t>
+          <t>-56,34; 273,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 461,57</t>
+          <t>16,34; 489,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,54; 282,49</t>
+          <t>-37,56; 269,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,48; 200,74</t>
+          <t>-39,66; 240,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 219,46</t>
+          <t>-24,91; 209,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 188,67</t>
+          <t>-19,32; 189,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 164,51</t>
+          <t>-22,37; 161,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,7; 249,24</t>
+          <t>21,21; 256,11</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,14</t>
+          <t>5,94</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>5,86</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,15</t>
+          <t>-0,82; 3,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,9</t>
+          <t>-1,24; 2,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 7,02</t>
+          <t>3,13; 8,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 3,4</t>
+          <t>-5,25; 3,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 6,59</t>
+          <t>-4,23; 6,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 10,5</t>
+          <t>0,99; 10,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,71</t>
+          <t>-1,22; 2,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,13</t>
+          <t>-1,05; 3,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 6,74</t>
+          <t>3,57; 8,34</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134,97%</t>
+          <t>253,89%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>115,31%</t>
+          <t>111,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>118,84%</t>
+          <t>198,85%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,62; 225,07</t>
+          <t>-31,91; 208,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,45; 225,73</t>
+          <t>-44,1; 211,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 402,85</t>
+          <t>73,62; 576,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,45; 123,08</t>
+          <t>-67,81; 127,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,91; 218,65</t>
+          <t>-62,64; 213,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 322,97</t>
+          <t>6,59; 331,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 130,77</t>
+          <t>-30,45; 125,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 152,1</t>
+          <t>-31,97; 139,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 271,52</t>
+          <t>85,26; 400,57</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>4,1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>3,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,02</t>
+          <t>0,62; 4,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,28</t>
+          <t>-2,28; 0,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,13</t>
+          <t>1,94; 5,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,34</t>
+          <t>-0,54; 3,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,73</t>
+          <t>-1,08; 2,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 5,09</t>
+          <t>2,16; 5,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,09</t>
+          <t>0,61; 3,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,76</t>
+          <t>-1,28; 0,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,36</t>
+          <t>2,49; 4,97</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>109,66%</t>
+          <t>115,23%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>139,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>101,77%</t>
+          <t>124,78%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,82; 169,24</t>
+          <t>11,84; 163,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-59,51; 13,94</t>
+          <t>-61,29; 15,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,34; 216,76</t>
+          <t>43,63; 227,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 150,12</t>
+          <t>-15,53; 171,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 134,62</t>
+          <t>-29,76; 134,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 215,18</t>
+          <t>47,97; 273,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,18; 123,48</t>
+          <t>15,83; 130,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,41; 30,28</t>
+          <t>-36,51; 33,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34,96; 170,53</t>
+          <t>67,58; 202,66</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>2,95</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>9,16</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,6</t>
+          <t>6,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,62</t>
+          <t>-1,83; 3,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,43</t>
+          <t>-1,49; 3,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,14; 8,28</t>
+          <t>0,2; 5,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,19</t>
+          <t>1,21; 6,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,55</t>
+          <t>-1,59; 2,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,08; 10,34</t>
+          <t>6,74; 11,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,4</t>
+          <t>0,9; 4,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,32</t>
+          <t>-0,93; 2,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,68</t>
+          <t>4,71; 8,27</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133,67%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>258,18%</t>
+          <t>297,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>212,23%</t>
+          <t>213,65%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-38,96; 217,74</t>
+          <t>-41,1; 185,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,8; 179,45</t>
+          <t>-35,92; 172,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13,29; 369,81</t>
+          <t>-1,46; 294,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32,69; 328,95</t>
+          <t>22,49; 279,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,05; 121,3</t>
+          <t>-39,63; 108,92</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,53; 508,57</t>
+          <t>138,7; 564,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,23; 192,67</t>
+          <t>18,81; 191,59</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 103,21</t>
+          <t>-24,06; 103,13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>115,34; 372,61</t>
+          <t>107,63; 367,36</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,21</t>
+          <t>4,22</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,66</t>
+          <t>-0,62; 3,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,82</t>
+          <t>-1,48; 0,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,92</t>
+          <t>-0,75; 2,8</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,33</t>
+          <t>-1,13; 2,45</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,86</t>
+          <t>-1,74; 2,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,46</t>
+          <t>3,23; 7,32</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,38</t>
+          <t>-0,89; 2,14</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,35</t>
+          <t>-1,44; 1,44</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,96</t>
+          <t>2,61; 5,8</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113,56%</t>
+          <t>111,05%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>121,02%</t>
+          <t>116,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>110,06%</t>
+          <t>110,24%</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-97,37; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-21,97; 62,79</t>
+          <t>-20,86; 63,71</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-30,81; 51,67</t>
+          <t>-32,31; 53,06</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>60,16; 198,84</t>
+          <t>57,47; 193,14</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 75,26</t>
+          <t>-20,5; 69,38</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-34,98; 42,17</t>
+          <t>-32,11; 46,77</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53,54; 190,76</t>
+          <t>53,72; 189,8</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,36</t>
+          <t>3,59</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>4,9</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>4,27</t>
         </is>
       </c>
     </row>
@@ -1973,37 +1973,37 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,32</t>
+          <t>0,45; 2,42</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,09</t>
+          <t>-0,53; 1,14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,44</t>
+          <t>2,67; 4,6</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,78</t>
+          <t>0,66; 2,79</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,46</t>
+          <t>-0,46; 1,39</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,36</t>
+          <t>3,95; 5,91</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,3</t>
+          <t>0,89; 2,26</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,63</t>
+          <t>3,57; 4,89</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>126,79%</t>
+          <t>135,56%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>120,0%</t>
+          <t>136,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>123,2%</t>
+          <t>136,31%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>17,31; 101,16</t>
+          <t>14,81; 107,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 48,34</t>
+          <t>-18,61; 52,61</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>69,21; 188,84</t>
+          <t>83,5; 211,55</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18,01; 87,86</t>
+          <t>15,45; 88,13</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 45,28</t>
+          <t>-11,63; 43,36</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>72,17; 166,58</t>
+          <t>95,59; 192,86</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,16; 81,38</t>
+          <t>25,88; 78,96</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 33,83</t>
+          <t>-7,58; 34,7</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>85,87; 167,12</t>
+          <t>101,64; 171,33</t>
         </is>
       </c>
     </row>
